--- a/public/sap-reporting/expansion-150-downloads/EXT-FI30-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-FI30-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Re1ee105059d04537"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R2f634b92bc9e4c25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Re481d53f31814bca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R557b20f4702f4a93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R6f56fcaf1a9e4463"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R14047225d01a4d62"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -506,10 +506,10 @@
         <x:v>0000100001</x:v>
       </x:c>
       <x:c r="O7" s="2" t="str">
-        <x:v>0000100001</x:v>
+        <x:v>1000.00</x:v>
       </x:c>
       <x:c r="P7" s="2" t="str">
-        <x:v>0000100001</x:v>
+        <x:v>1100.00</x:v>
       </x:c>
       <x:c r="Q7" s="2" t="str">
         <x:v>OPEN</x:v>
@@ -557,10 +557,10 @@
         <x:v>0000100002</x:v>
       </x:c>
       <x:c r="O8" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="P8" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="Q8" s="2" t="str">
         <x:v>EXCEPTION</x:v>
@@ -610,10 +610,10 @@
         <x:v>0000100003</x:v>
       </x:c>
       <x:c r="O9" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="P9" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="Q9" s="2" t="str">
         <x:v>REVIEW</x:v>
@@ -663,10 +663,10 @@
         <x:v>0000100004</x:v>
       </x:c>
       <x:c r="O10" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="P10" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="Q10" s="2" t="str">
         <x:v>DUPLICATE_TEST</x:v>
@@ -807,10 +807,10 @@
         <x:v>0000100001</x:v>
       </x:c>
       <x:c r="O2" s="2" t="str">
-        <x:v>0000100001</x:v>
+        <x:v>1000.00</x:v>
       </x:c>
       <x:c r="P2" s="2" t="str">
-        <x:v>0000100001</x:v>
+        <x:v>1100.00</x:v>
       </x:c>
       <x:c r="Q2" s="2" t="str">
         <x:v>OPEN</x:v>
@@ -858,10 +858,10 @@
         <x:v>0000100002</x:v>
       </x:c>
       <x:c r="O3" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="P3" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="Q3" s="2" t="str">
         <x:v>EXCEPTION</x:v>
@@ -911,10 +911,10 @@
         <x:v>0000100003</x:v>
       </x:c>
       <x:c r="O4" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="P4" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="Q4" s="2" t="str">
         <x:v>REVIEW</x:v>
@@ -964,10 +964,10 @@
         <x:v>0000100004</x:v>
       </x:c>
       <x:c r="O5" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="P5" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="Q5" s="2" t="str">
         <x:v>DUPLICATE_TEST</x:v>
@@ -1293,7 +1293,7 @@
         <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="63" customHeight="1">
+    <x:row r="16" ht="80" customHeight="1">
       <x:c r="A16" s="8" t="str">
         <x:v>15</x:v>
       </x:c>
@@ -1301,7 +1301,7 @@
         <x:v>Opening Balance</x:v>
       </x:c>
       <x:c r="C16" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>raw_decimal</x:v>
       </x:c>
       <x:c r="D16" s="8" t="str">
         <x:v>Số dư đầu kỳ; không cộng snapshot</x:v>
@@ -1310,10 +1310,10 @@
         <x:v>SAVA_PROPOSED / chưa xác minh</x:v>
       </x:c>
       <x:c r="F16" s="8" t="str">
-        <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="63" customHeight="1">
+        <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="80" customHeight="1">
       <x:c r="A17" s="8" t="str">
         <x:v>16</x:v>
       </x:c>
@@ -1321,7 +1321,7 @@
         <x:v>Closing Balance</x:v>
       </x:c>
       <x:c r="C17" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>raw_decimal</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
         <x:v>Số dư cuối kỳ; không cộng snapshot</x:v>
@@ -1330,7 +1330,7 @@
         <x:v>SAVA_PROPOSED / chưa xác minh</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
+        <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="63" customHeight="1">
